--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU02/HRM/post FET_HRM-2031-0132/Panel 7/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU02/HRM/post FET_HRM-2031-0132/Panel 7/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.83696</v>
+        <v>16.79345</v>
       </c>
       <c r="D2" t="n">
-        <v>16.46374</v>
+        <v>16.40202</v>
       </c>
       <c r="E2" t="n">
-        <v>16.84607</v>
+        <v>16.54834</v>
       </c>
       <c r="F2" t="n">
-        <v>43.06726</v>
+        <v>42.01069</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05119</v>
+        <v>0.05098</v>
       </c>
       <c r="H2" t="n">
-        <v>1.8273</v>
+        <v>1.82813</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.04377</v>
+        <v>16.85946</v>
       </c>
       <c r="D3" t="n">
-        <v>16.53231</v>
+        <v>16.33119</v>
       </c>
       <c r="E3" t="n">
-        <v>16.99571</v>
+        <v>16.85411</v>
       </c>
       <c r="F3" t="n">
-        <v>42.85681</v>
+        <v>42.11453</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05147</v>
+        <v>0.05092</v>
       </c>
       <c r="H3" t="n">
-        <v>1.80294</v>
+        <v>1.81047</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.66973</v>
+        <v>17.12431</v>
       </c>
       <c r="D4" t="n">
-        <v>16.63189</v>
+        <v>16.59621</v>
       </c>
       <c r="E4" t="n">
-        <v>16.58685</v>
+        <v>16.66188</v>
       </c>
       <c r="F4" t="n">
-        <v>42.43948</v>
+        <v>42.19892</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05008</v>
+        <v>0.05002</v>
       </c>
       <c r="H4" t="n">
-        <v>1.79493</v>
+        <v>1.86315</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.45002</v>
+        <v>16.58036</v>
       </c>
       <c r="D6" t="n">
-        <v>16.06265</v>
+        <v>16.03875</v>
       </c>
       <c r="E6" t="n">
-        <v>16.5733</v>
+        <v>16.44508</v>
       </c>
       <c r="F6" t="n">
-        <v>22.07863</v>
+        <v>21.8529</v>
       </c>
       <c r="G6" t="n">
-        <v>33.40257</v>
+        <v>33.69726</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.54463</v>
+        <v>16.70831</v>
       </c>
       <c r="D7" t="n">
-        <v>15.99689</v>
+        <v>15.85414</v>
       </c>
       <c r="E7" t="n">
-        <v>16.09707</v>
+        <v>16.50938</v>
       </c>
       <c r="F7" t="n">
-        <v>21.72859</v>
+        <v>21.72265</v>
       </c>
       <c r="G7" t="n">
-        <v>34.57993</v>
+        <v>34.48572</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.62652</v>
+        <v>16.68486</v>
       </c>
       <c r="D8" t="n">
-        <v>15.90204</v>
+        <v>16.24833</v>
       </c>
       <c r="E8" t="n">
-        <v>16.51844</v>
+        <v>16.34387</v>
       </c>
       <c r="F8" t="n">
-        <v>22.00574</v>
+        <v>22.16866</v>
       </c>
       <c r="G8" t="n">
-        <v>34.14127</v>
+        <v>33.39412</v>
       </c>
     </row>
     <row r="9">
@@ -650,10 +650,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.60216</v>
+        <v>0.59402</v>
       </c>
       <c r="D10" t="n">
-        <v>1.10783</v>
+        <v>1.11659</v>
       </c>
     </row>
     <row r="11">
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.61524</v>
+        <v>0.6207</v>
       </c>
       <c r="D11" t="n">
-        <v>1.13841</v>
+        <v>1.1237</v>
       </c>
     </row>
     <row r="12">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.61033</v>
+        <v>0.61224</v>
       </c>
       <c r="D12" t="n">
-        <v>1.13767</v>
+        <v>1.10114</v>
       </c>
     </row>
   </sheetData>
